--- a/IV_5.5K_T2.xlsx
+++ b/IV_5.5K_T2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -6384,7 +6384,7 @@
         <v>-90.625</v>
       </c>
       <c r="F191">
-        <v>-0.15866</v>
+        <v>-0.15865000000000001</v>
       </c>
       <c r="G191">
         <v>-90.625</v>
@@ -6416,7 +6416,7 @@
         <v>-92.1875</v>
       </c>
       <c r="F192">
-        <v>-0.16142000000000001</v>
+        <v>-0.16141</v>
       </c>
       <c r="G192">
         <v>-92.1875</v>
@@ -6480,7 +6480,7 @@
         <v>-95.3125</v>
       </c>
       <c r="F194">
-        <v>-0.16693</v>
+        <v>-0.16694999999999999</v>
       </c>
       <c r="G194">
         <v>-95.3125</v>
@@ -7376,7 +7376,7 @@
         <v>-60.9375</v>
       </c>
       <c r="F222">
-        <v>-0.10679</v>
+        <v>-0.10677</v>
       </c>
       <c r="G222">
         <v>-60.9375</v>
@@ -7472,7 +7472,7 @@
         <v>-56.25</v>
       </c>
       <c r="F225">
-        <v>-9.8559999999999995E-2</v>
+        <v>-9.8519999999999996E-2</v>
       </c>
       <c r="G225">
         <v>-56.25</v>
@@ -7524,7 +7524,7 @@
         <v>-53.125</v>
       </c>
       <c r="B227">
-        <v>-9.3090000000000006E-2</v>
+        <v>-9.3079999999999996E-2</v>
       </c>
       <c r="C227">
         <v>-53.125</v>
@@ -7708,7 +7708,7 @@
         <v>-45.3125</v>
       </c>
       <c r="J232">
-        <v>-7.9140000000000002E-2</v>
+        <v>-7.9149999999999998E-2</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
@@ -7728,7 +7728,7 @@
         <v>-43.75</v>
       </c>
       <c r="F233">
-        <v>-7.6569999999999999E-2</v>
+        <v>-7.6579999999999995E-2</v>
       </c>
       <c r="G233">
         <v>-43.75</v>
@@ -7772,7 +7772,7 @@
         <v>-42.1875</v>
       </c>
       <c r="J234">
-        <v>-7.3669999999999999E-2</v>
+        <v>-7.3690000000000005E-2</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -7792,13 +7792,13 @@
         <v>-40.625</v>
       </c>
       <c r="F235">
-        <v>-7.1099999999999997E-2</v>
+        <v>-7.1110000000000007E-2</v>
       </c>
       <c r="G235">
         <v>-40.625</v>
       </c>
       <c r="H235">
-        <v>-7.0910000000000001E-2</v>
+        <v>-7.0900000000000005E-2</v>
       </c>
       <c r="I235">
         <v>-40.625</v>
